--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300336</v>
+        <v>128300334</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>82873</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898991</v>
+        <v>898973</v>
       </c>
       <c r="R2" t="n">
-        <v>7340368</v>
+        <v>7340375</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300334</v>
+        <v>128300336</v>
       </c>
       <c r="B3" t="n">
-        <v>82870</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898973</v>
+        <v>898991</v>
       </c>
       <c r="R3" t="n">
-        <v>7340375</v>
+        <v>7340368</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -872,7 +872,7 @@
         <v>128300382</v>
       </c>
       <c r="B4" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128300368</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128300365</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128300341</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128300386</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128300381</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128300342</v>
       </c>
       <c r="B10" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128300330</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128300335</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128300367</v>
       </c>
       <c r="B13" t="n">
-        <v>79053</v>
+        <v>79056</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128300383</v>
       </c>
       <c r="B14" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128300380</v>
       </c>
       <c r="B15" t="n">
-        <v>82870</v>
+        <v>82873</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128300339</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300332</v>
+        <v>128300333</v>
       </c>
       <c r="B17" t="n">
-        <v>97347</v>
+        <v>82873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898948</v>
+        <v>898956</v>
       </c>
       <c r="R17" t="n">
-        <v>7340405</v>
+        <v>7340380</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128300333</v>
+        <v>128300385</v>
       </c>
       <c r="B18" t="n">
-        <v>82870</v>
+        <v>79032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>898956</v>
+        <v>898974</v>
       </c>
       <c r="R18" t="n">
-        <v>7340380</v>
+        <v>7340314</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128300385</v>
+        <v>128300332</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>97355</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>898974</v>
+        <v>898948</v>
       </c>
       <c r="R19" t="n">
-        <v>7340314</v>
+        <v>7340405</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2424,7 +2424,7 @@
         <v>128300366</v>
       </c>
       <c r="B20" t="n">
-        <v>91317</v>
+        <v>91325</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128300364</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128300340</v>
       </c>
       <c r="B22" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128300338</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128300331</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128300369</v>
       </c>
       <c r="B25" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>128300370</v>
       </c>
       <c r="B26" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128300334</v>
       </c>
       <c r="B2" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128300336</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300382</v>
+        <v>128300368</v>
       </c>
       <c r="B4" t="n">
-        <v>91325</v>
+        <v>79702</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>898974</v>
+        <v>898675</v>
       </c>
       <c r="R4" t="n">
-        <v>7340306</v>
+        <v>7340362</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,17 +959,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300368</v>
+        <v>128300365</v>
       </c>
       <c r="B5" t="n">
-        <v>79650</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>898675</v>
+        <v>898914</v>
       </c>
       <c r="R5" t="n">
-        <v>7340362</v>
+        <v>7340380</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1056,39 +1056,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128300365</v>
+        <v>128300382</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>91417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>898914</v>
+        <v>898974</v>
       </c>
       <c r="R6" t="n">
-        <v>7340380</v>
+        <v>7340306</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>128300341</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128300386</v>
       </c>
       <c r="B8" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
         <v>128300381</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
         <v>128300342</v>
       </c>
       <c r="B10" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128300330</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128300335</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128300367</v>
       </c>
       <c r="B13" t="n">
-        <v>79056</v>
+        <v>79107</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
         <v>128300383</v>
       </c>
       <c r="B14" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
         <v>128300380</v>
       </c>
       <c r="B15" t="n">
-        <v>82873</v>
+        <v>82942</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2036,7 +2036,7 @@
         <v>128300339</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300333</v>
+        <v>128300332</v>
       </c>
       <c r="B17" t="n">
-        <v>82873</v>
+        <v>97448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898956</v>
+        <v>898948</v>
       </c>
       <c r="R17" t="n">
-        <v>7340380</v>
+        <v>7340405</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2230,7 +2230,7 @@
         <v>128300385</v>
       </c>
       <c r="B18" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2317,39 +2317,39 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128300332</v>
+        <v>128300333</v>
       </c>
       <c r="B19" t="n">
-        <v>97355</v>
+        <v>82942</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>898948</v>
+        <v>898956</v>
       </c>
       <c r="R19" t="n">
-        <v>7340405</v>
+        <v>7340380</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2424,7 +2424,7 @@
         <v>128300366</v>
       </c>
       <c r="B20" t="n">
-        <v>91325</v>
+        <v>91417</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2521,7 +2521,7 @@
         <v>128300364</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2618,7 +2618,7 @@
         <v>128300340</v>
       </c>
       <c r="B22" t="n">
-        <v>97355</v>
+        <v>97448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128300338</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128300331</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128300369</v>
       </c>
       <c r="B25" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3006,7 +3006,7 @@
         <v>128300370</v>
       </c>
       <c r="B26" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300334</v>
+        <v>128300336</v>
       </c>
       <c r="B2" t="n">
-        <v>82942</v>
+        <v>79083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898973</v>
+        <v>898991</v>
       </c>
       <c r="R2" t="n">
-        <v>7340375</v>
+        <v>7340368</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300336</v>
+        <v>128300334</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>82942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898991</v>
+        <v>898973</v>
       </c>
       <c r="R3" t="n">
-        <v>7340368</v>
+        <v>7340375</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128300386</v>
+        <v>128300381</v>
       </c>
       <c r="B8" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>898950</v>
+        <v>898984</v>
       </c>
       <c r="R8" t="n">
-        <v>7340336</v>
+        <v>7340282</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128300381</v>
+        <v>128300386</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>898984</v>
+        <v>898950</v>
       </c>
       <c r="R9" t="n">
-        <v>7340282</v>
+        <v>7340336</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128300342</v>
+        <v>128300330</v>
       </c>
       <c r="B10" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>899019</v>
+        <v>898890</v>
       </c>
       <c r="R10" t="n">
-        <v>7340290</v>
+        <v>7340453</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128300330</v>
+        <v>128300342</v>
       </c>
       <c r="B11" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>898890</v>
+        <v>899019</v>
       </c>
       <c r="R11" t="n">
-        <v>7340453</v>
+        <v>7340290</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300332</v>
+        <v>128300333</v>
       </c>
       <c r="B17" t="n">
-        <v>97448</v>
+        <v>82942</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898948</v>
+        <v>898956</v>
       </c>
       <c r="R17" t="n">
-        <v>7340405</v>
+        <v>7340380</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128300333</v>
+        <v>128300332</v>
       </c>
       <c r="B19" t="n">
-        <v>82942</v>
+        <v>97448</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>898956</v>
+        <v>898948</v>
       </c>
       <c r="R19" t="n">
-        <v>7340380</v>
+        <v>7340405</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128300369</v>
+        <v>128300370</v>
       </c>
       <c r="B25" t="n">
         <v>79702</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>898684</v>
+        <v>898703</v>
       </c>
       <c r="R25" t="n">
-        <v>7340341</v>
+        <v>7340339</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3003,7 +3003,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128300370</v>
+        <v>128300369</v>
       </c>
       <c r="B26" t="n">
         <v>79702</v>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>898703</v>
+        <v>898684</v>
       </c>
       <c r="R26" t="n">
-        <v>7340339</v>
+        <v>7340341</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300336</v>
+        <v>128300334</v>
       </c>
       <c r="B2" t="n">
-        <v>79083</v>
+        <v>82942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898991</v>
+        <v>898973</v>
       </c>
       <c r="R2" t="n">
-        <v>7340368</v>
+        <v>7340375</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300334</v>
+        <v>128300336</v>
       </c>
       <c r="B3" t="n">
-        <v>82942</v>
+        <v>79083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898973</v>
+        <v>898991</v>
       </c>
       <c r="R3" t="n">
-        <v>7340375</v>
+        <v>7340368</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300368</v>
+        <v>128300365</v>
       </c>
       <c r="B4" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>898675</v>
+        <v>898914</v>
       </c>
       <c r="R4" t="n">
-        <v>7340362</v>
+        <v>7340380</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,17 +959,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300365</v>
+        <v>128300368</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>898914</v>
+        <v>898675</v>
       </c>
       <c r="R5" t="n">
-        <v>7340380</v>
+        <v>7340362</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128300381</v>
+        <v>128300386</v>
       </c>
       <c r="B8" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>898984</v>
+        <v>898950</v>
       </c>
       <c r="R8" t="n">
-        <v>7340282</v>
+        <v>7340336</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128300386</v>
+        <v>128300381</v>
       </c>
       <c r="B9" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>898950</v>
+        <v>898984</v>
       </c>
       <c r="R9" t="n">
-        <v>7340336</v>
+        <v>7340282</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128300331</v>
+        <v>128300369</v>
       </c>
       <c r="B24" t="n">
-        <v>79083</v>
+        <v>79702</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>898938</v>
+        <v>898684</v>
       </c>
       <c r="R24" t="n">
-        <v>7340414</v>
+        <v>7340341</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2996,17 +2996,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128300369</v>
+        <v>128300331</v>
       </c>
       <c r="B26" t="n">
-        <v>79702</v>
+        <v>79083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>898684</v>
+        <v>898938</v>
       </c>
       <c r="R26" t="n">
-        <v>7340341</v>
+        <v>7340414</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128300334</v>
       </c>
       <c r="B2" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128300336</v>
       </c>
       <c r="B3" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300365</v>
+        <v>128300368</v>
       </c>
       <c r="B4" t="n">
-        <v>79083</v>
+        <v>79706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>898914</v>
+        <v>898675</v>
       </c>
       <c r="R4" t="n">
-        <v>7340380</v>
+        <v>7340362</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300368</v>
+        <v>128300365</v>
       </c>
       <c r="B5" t="n">
-        <v>79702</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>898675</v>
+        <v>898914</v>
       </c>
       <c r="R5" t="n">
-        <v>7340362</v>
+        <v>7340380</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
         <v>128300382</v>
       </c>
       <c r="B6" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128300341</v>
       </c>
       <c r="B7" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128300386</v>
       </c>
       <c r="B8" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128300381</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128300330</v>
+        <v>128300342</v>
       </c>
       <c r="B10" t="n">
-        <v>79083</v>
+        <v>79706</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>898890</v>
+        <v>899019</v>
       </c>
       <c r="R10" t="n">
-        <v>7340453</v>
+        <v>7340290</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128300342</v>
+        <v>128300330</v>
       </c>
       <c r="B11" t="n">
-        <v>79702</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>899019</v>
+        <v>898890</v>
       </c>
       <c r="R11" t="n">
-        <v>7340290</v>
+        <v>7340453</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1648,7 +1648,7 @@
         <v>128300335</v>
       </c>
       <c r="B12" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128300367</v>
       </c>
       <c r="B13" t="n">
-        <v>79107</v>
+        <v>79111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128300383</v>
       </c>
       <c r="B14" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128300380</v>
       </c>
       <c r="B15" t="n">
-        <v>82942</v>
+        <v>82946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128300339</v>
       </c>
       <c r="B16" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300333</v>
+        <v>128300385</v>
       </c>
       <c r="B17" t="n">
-        <v>82942</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898956</v>
+        <v>898974</v>
       </c>
       <c r="R17" t="n">
-        <v>7340380</v>
+        <v>7340314</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128300385</v>
+        <v>128300333</v>
       </c>
       <c r="B18" t="n">
-        <v>79083</v>
+        <v>82946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>898974</v>
+        <v>898956</v>
       </c>
       <c r="R18" t="n">
-        <v>7340314</v>
+        <v>7340380</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2327,7 +2327,7 @@
         <v>128300332</v>
       </c>
       <c r="B19" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128300366</v>
       </c>
       <c r="B20" t="n">
-        <v>91417</v>
+        <v>91429</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128300364</v>
       </c>
       <c r="B21" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128300340</v>
       </c>
       <c r="B22" t="n">
-        <v>97448</v>
+        <v>97460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128300338</v>
       </c>
       <c r="B23" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128300369</v>
+        <v>128300331</v>
       </c>
       <c r="B24" t="n">
-        <v>79702</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>898684</v>
+        <v>898938</v>
       </c>
       <c r="R24" t="n">
-        <v>7340341</v>
+        <v>7340414</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128300370</v>
+        <v>128300369</v>
       </c>
       <c r="B25" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>898703</v>
+        <v>898684</v>
       </c>
       <c r="R25" t="n">
-        <v>7340339</v>
+        <v>7340341</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128300331</v>
+        <v>128300370</v>
       </c>
       <c r="B26" t="n">
-        <v>79083</v>
+        <v>79706</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>898938</v>
+        <v>898703</v>
       </c>
       <c r="R26" t="n">
-        <v>7340414</v>
+        <v>7340339</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300334</v>
+        <v>128300336</v>
       </c>
       <c r="B2" t="n">
-        <v>82946</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898973</v>
+        <v>898991</v>
       </c>
       <c r="R2" t="n">
-        <v>7340375</v>
+        <v>7340368</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300336</v>
+        <v>128300334</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>82946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898991</v>
+        <v>898973</v>
       </c>
       <c r="R3" t="n">
-        <v>7340368</v>
+        <v>7340375</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300385</v>
+        <v>128300333</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>82946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898974</v>
+        <v>898956</v>
       </c>
       <c r="R17" t="n">
-        <v>7340314</v>
+        <v>7340380</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128300333</v>
+        <v>128300385</v>
       </c>
       <c r="B18" t="n">
-        <v>82946</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>898956</v>
+        <v>898974</v>
       </c>
       <c r="R18" t="n">
-        <v>7340380</v>
+        <v>7340314</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300336</v>
+        <v>128300334</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>82948</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898991</v>
+        <v>898973</v>
       </c>
       <c r="R2" t="n">
-        <v>7340368</v>
+        <v>7340375</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300334</v>
+        <v>128300336</v>
       </c>
       <c r="B3" t="n">
-        <v>82946</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898973</v>
+        <v>898991</v>
       </c>
       <c r="R3" t="n">
-        <v>7340375</v>
+        <v>7340368</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300368</v>
+        <v>128300382</v>
       </c>
       <c r="B4" t="n">
-        <v>79706</v>
+        <v>91431</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>898675</v>
+        <v>898974</v>
       </c>
       <c r="R4" t="n">
-        <v>7340362</v>
+        <v>7340306</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128300365</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,39 +1056,39 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128300382</v>
+        <v>128300368</v>
       </c>
       <c r="B6" t="n">
-        <v>91429</v>
+        <v>79708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>898974</v>
+        <v>898675</v>
       </c>
       <c r="R6" t="n">
-        <v>7340306</v>
+        <v>7340362</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>128300341</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128300386</v>
+        <v>128300381</v>
       </c>
       <c r="B8" t="n">
-        <v>79706</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>898950</v>
+        <v>898984</v>
       </c>
       <c r="R8" t="n">
-        <v>7340336</v>
+        <v>7340282</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128300381</v>
+        <v>128300386</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>898984</v>
+        <v>898950</v>
       </c>
       <c r="R9" t="n">
-        <v>7340282</v>
+        <v>7340336</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1444,17 +1444,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128300342</v>
+        <v>128300330</v>
       </c>
       <c r="B10" t="n">
-        <v>79706</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>899019</v>
+        <v>898890</v>
       </c>
       <c r="R10" t="n">
-        <v>7340290</v>
+        <v>7340453</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128300330</v>
+        <v>128300342</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>79708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>898890</v>
+        <v>899019</v>
       </c>
       <c r="R11" t="n">
-        <v>7340453</v>
+        <v>7340290</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1648,7 +1648,7 @@
         <v>128300335</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128300367</v>
       </c>
       <c r="B13" t="n">
-        <v>79111</v>
+        <v>79113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
         <v>128300383</v>
       </c>
       <c r="B14" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
         <v>128300380</v>
       </c>
       <c r="B15" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2036,7 +2036,7 @@
         <v>128300339</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>128300333</v>
       </c>
       <c r="B17" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>128300385</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2327,7 +2327,7 @@
         <v>128300332</v>
       </c>
       <c r="B19" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128300366</v>
       </c>
       <c r="B20" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2521,7 +2521,7 @@
         <v>128300364</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2618,7 +2618,7 @@
         <v>128300340</v>
       </c>
       <c r="B22" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128300338</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128300331</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128300369</v>
       </c>
       <c r="B25" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3006,7 +3006,7 @@
         <v>128300370</v>
       </c>
       <c r="B26" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -959,17 +959,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300365</v>
+        <v>128300368</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>898914</v>
+        <v>898675</v>
       </c>
       <c r="R5" t="n">
-        <v>7340380</v>
+        <v>7340362</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128300368</v>
+        <v>128300365</v>
       </c>
       <c r="B6" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>898675</v>
+        <v>898914</v>
       </c>
       <c r="R6" t="n">
-        <v>7340362</v>
+        <v>7340380</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128300381</v>
+        <v>128300386</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>898984</v>
+        <v>898950</v>
       </c>
       <c r="R8" t="n">
-        <v>7340282</v>
+        <v>7340336</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128300386</v>
+        <v>128300381</v>
       </c>
       <c r="B9" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>898950</v>
+        <v>898984</v>
       </c>
       <c r="R9" t="n">
-        <v>7340336</v>
+        <v>7340282</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1444,17 +1444,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128300330</v>
+        <v>128300342</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>898890</v>
+        <v>899019</v>
       </c>
       <c r="R10" t="n">
-        <v>7340453</v>
+        <v>7340290</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128300342</v>
+        <v>128300330</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>899019</v>
+        <v>898890</v>
       </c>
       <c r="R11" t="n">
-        <v>7340290</v>
+        <v>7340453</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2317,7 +2317,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300334</v>
+        <v>128300336</v>
       </c>
       <c r="B2" t="n">
-        <v>82948</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898973</v>
+        <v>898991</v>
       </c>
       <c r="R2" t="n">
-        <v>7340375</v>
+        <v>7340368</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300336</v>
+        <v>128300334</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>82948</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898991</v>
+        <v>898973</v>
       </c>
       <c r="R3" t="n">
-        <v>7340368</v>
+        <v>7340375</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128300382</v>
       </c>
       <c r="B4" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128300386</v>
+        <v>128300381</v>
       </c>
       <c r="B8" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>898950</v>
+        <v>898984</v>
       </c>
       <c r="R8" t="n">
-        <v>7340336</v>
+        <v>7340282</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128300381</v>
+        <v>128300386</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>898984</v>
+        <v>898950</v>
       </c>
       <c r="R9" t="n">
-        <v>7340282</v>
+        <v>7340336</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128300342</v>
+        <v>128300330</v>
       </c>
       <c r="B10" t="n">
-        <v>79708</v>
+        <v>79089</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>899019</v>
+        <v>898890</v>
       </c>
       <c r="R10" t="n">
-        <v>7340290</v>
+        <v>7340453</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128300330</v>
+        <v>128300342</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>898890</v>
+        <v>899019</v>
       </c>
       <c r="R11" t="n">
-        <v>7340453</v>
+        <v>7340290</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2327,7 +2327,7 @@
         <v>128300332</v>
       </c>
       <c r="B19" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128300366</v>
       </c>
       <c r="B20" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128300340</v>
       </c>
       <c r="B22" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300382</v>
+        <v>128300365</v>
       </c>
       <c r="B4" t="n">
-        <v>91432</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>898974</v>
+        <v>898914</v>
       </c>
       <c r="R4" t="n">
-        <v>7340306</v>
+        <v>7340380</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300368</v>
+        <v>128300382</v>
       </c>
       <c r="B5" t="n">
-        <v>79708</v>
+        <v>91432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>898675</v>
+        <v>898974</v>
       </c>
       <c r="R5" t="n">
-        <v>7340362</v>
+        <v>7340306</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128300365</v>
+        <v>128300368</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>79708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>898914</v>
+        <v>898675</v>
       </c>
       <c r="R6" t="n">
-        <v>7340380</v>
+        <v>7340362</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128300336</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128300334</v>
       </c>
       <c r="B3" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300365</v>
+        <v>128300382</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>91459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>898914</v>
+        <v>898974</v>
       </c>
       <c r="R4" t="n">
-        <v>7340380</v>
+        <v>7340306</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,39 +959,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300382</v>
+        <v>128300368</v>
       </c>
       <c r="B5" t="n">
-        <v>91432</v>
+        <v>79735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>898974</v>
+        <v>898675</v>
       </c>
       <c r="R5" t="n">
-        <v>7340306</v>
+        <v>7340362</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1056,17 +1056,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128300368</v>
+        <v>128300365</v>
       </c>
       <c r="B6" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>898675</v>
+        <v>898914</v>
       </c>
       <c r="R6" t="n">
-        <v>7340362</v>
+        <v>7340380</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>128300341</v>
       </c>
       <c r="B7" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128300381</v>
       </c>
       <c r="B8" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
         <v>128300386</v>
       </c>
       <c r="B9" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,17 +1444,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128300330</v>
+        <v>128300342</v>
       </c>
       <c r="B10" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>898890</v>
+        <v>899019</v>
       </c>
       <c r="R10" t="n">
-        <v>7340453</v>
+        <v>7340290</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128300342</v>
+        <v>128300330</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>899019</v>
+        <v>898890</v>
       </c>
       <c r="R11" t="n">
-        <v>7340290</v>
+        <v>7340453</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1648,7 +1648,7 @@
         <v>128300335</v>
       </c>
       <c r="B12" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128300367</v>
       </c>
       <c r="B13" t="n">
-        <v>79113</v>
+        <v>79140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1842,7 +1842,7 @@
         <v>128300383</v>
       </c>
       <c r="B14" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
         <v>128300380</v>
       </c>
       <c r="B15" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2036,7 +2036,7 @@
         <v>128300339</v>
       </c>
       <c r="B16" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300333</v>
+        <v>128300385</v>
       </c>
       <c r="B17" t="n">
-        <v>82948</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898956</v>
+        <v>898974</v>
       </c>
       <c r="R17" t="n">
-        <v>7340380</v>
+        <v>7340314</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2220,17 +2220,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128300385</v>
+        <v>128300333</v>
       </c>
       <c r="B18" t="n">
-        <v>79089</v>
+        <v>82975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>898974</v>
+        <v>898956</v>
       </c>
       <c r="R18" t="n">
-        <v>7340314</v>
+        <v>7340380</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2327,7 +2327,7 @@
         <v>128300332</v>
       </c>
       <c r="B19" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>128300366</v>
       </c>
       <c r="B20" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2521,7 +2521,7 @@
         <v>128300364</v>
       </c>
       <c r="B21" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2618,7 +2618,7 @@
         <v>128300340</v>
       </c>
       <c r="B22" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128300338</v>
       </c>
       <c r="B23" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128300331</v>
+        <v>128300369</v>
       </c>
       <c r="B24" t="n">
-        <v>79089</v>
+        <v>79735</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>898938</v>
+        <v>898684</v>
       </c>
       <c r="R24" t="n">
-        <v>7340414</v>
+        <v>7340341</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2899,17 +2899,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128300369</v>
+        <v>128300370</v>
       </c>
       <c r="B25" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>898684</v>
+        <v>898703</v>
       </c>
       <c r="R25" t="n">
-        <v>7340341</v>
+        <v>7340339</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -2996,17 +2996,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Tyrén, Jan Apelqvist</t>
+          <t>Jan Apelqvist, Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128300370</v>
+        <v>128300331</v>
       </c>
       <c r="B26" t="n">
-        <v>79708</v>
+        <v>79116</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>898703</v>
+        <v>898938</v>
       </c>
       <c r="R26" t="n">
-        <v>7340339</v>
+        <v>7340414</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300336</v>
+        <v>128300334</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>82975</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898991</v>
+        <v>898973</v>
       </c>
       <c r="R2" t="n">
-        <v>7340368</v>
+        <v>7340375</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300334</v>
+        <v>128300336</v>
       </c>
       <c r="B3" t="n">
-        <v>82975</v>
+        <v>79116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898973</v>
+        <v>898991</v>
       </c>
       <c r="R3" t="n">
-        <v>7340375</v>
+        <v>7340368</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128300381</v>
+        <v>128300386</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>79735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>898984</v>
+        <v>898950</v>
       </c>
       <c r="R8" t="n">
-        <v>7340282</v>
+        <v>7340336</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1347,17 +1347,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128300386</v>
+        <v>128300381</v>
       </c>
       <c r="B9" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>898950</v>
+        <v>898984</v>
       </c>
       <c r="R9" t="n">
-        <v>7340336</v>
+        <v>7340282</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300385</v>
+        <v>128300332</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>97490</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898974</v>
+        <v>898948</v>
       </c>
       <c r="R17" t="n">
-        <v>7340314</v>
+        <v>7340405</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2220,17 +2220,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128300333</v>
+        <v>128300385</v>
       </c>
       <c r="B18" t="n">
-        <v>82975</v>
+        <v>79116</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>898956</v>
+        <v>898974</v>
       </c>
       <c r="R18" t="n">
-        <v>7340380</v>
+        <v>7340314</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128300332</v>
+        <v>128300333</v>
       </c>
       <c r="B19" t="n">
-        <v>97490</v>
+        <v>82975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>898948</v>
+        <v>898956</v>
       </c>
       <c r="R19" t="n">
-        <v>7340405</v>
+        <v>7340380</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128300369</v>
+        <v>128300331</v>
       </c>
       <c r="B24" t="n">
-        <v>79735</v>
+        <v>79116</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>898684</v>
+        <v>898938</v>
       </c>
       <c r="R24" t="n">
-        <v>7340341</v>
+        <v>7340414</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2899,14 +2899,14 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128300370</v>
+        <v>128300369</v>
       </c>
       <c r="B25" t="n">
         <v>79735</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>898703</v>
+        <v>898684</v>
       </c>
       <c r="R25" t="n">
-        <v>7340339</v>
+        <v>7340341</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -2996,17 +2996,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Apelqvist, Håkan Tyrén</t>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128300331</v>
+        <v>128300370</v>
       </c>
       <c r="B26" t="n">
-        <v>79116</v>
+        <v>79735</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>898938</v>
+        <v>898703</v>
       </c>
       <c r="R26" t="n">
-        <v>7340414</v>
+        <v>7340339</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300334</v>
+        <v>128300336</v>
       </c>
       <c r="B2" t="n">
-        <v>82975</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898973</v>
+        <v>898991</v>
       </c>
       <c r="R2" t="n">
-        <v>7340375</v>
+        <v>7340368</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300336</v>
+        <v>128300334</v>
       </c>
       <c r="B3" t="n">
-        <v>79116</v>
+        <v>82979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898991</v>
+        <v>898973</v>
       </c>
       <c r="R3" t="n">
-        <v>7340368</v>
+        <v>7340375</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300382</v>
+        <v>128300365</v>
       </c>
       <c r="B4" t="n">
-        <v>91459</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>898974</v>
+        <v>898914</v>
       </c>
       <c r="R4" t="n">
-        <v>7340306</v>
+        <v>7340380</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +969,7 @@
         <v>128300368</v>
       </c>
       <c r="B5" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128300365</v>
+        <v>128300382</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>91469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>898914</v>
+        <v>898974</v>
       </c>
       <c r="R6" t="n">
-        <v>7340380</v>
+        <v>7340306</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1163,7 +1163,7 @@
         <v>128300341</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128300386</v>
       </c>
       <c r="B8" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128300381</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128300342</v>
       </c>
       <c r="B10" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128300330</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>128300335</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>128300367</v>
       </c>
       <c r="B13" t="n">
-        <v>79140</v>
+        <v>79144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>128300383</v>
       </c>
       <c r="B14" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>128300380</v>
       </c>
       <c r="B15" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>128300339</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300332</v>
+        <v>128300333</v>
       </c>
       <c r="B17" t="n">
-        <v>97490</v>
+        <v>82979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898948</v>
+        <v>898956</v>
       </c>
       <c r="R17" t="n">
-        <v>7340405</v>
+        <v>7340380</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2230,7 +2230,7 @@
         <v>128300385</v>
       </c>
       <c r="B18" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128300333</v>
+        <v>128300332</v>
       </c>
       <c r="B19" t="n">
-        <v>82975</v>
+        <v>97503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>898956</v>
+        <v>898948</v>
       </c>
       <c r="R19" t="n">
-        <v>7340380</v>
+        <v>7340405</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2424,7 +2424,7 @@
         <v>128300366</v>
       </c>
       <c r="B20" t="n">
-        <v>91459</v>
+        <v>91469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>128300364</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>128300340</v>
       </c>
       <c r="B22" t="n">
-        <v>97490</v>
+        <v>97503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>128300338</v>
       </c>
       <c r="B23" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>128300331</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>128300369</v>
       </c>
       <c r="B25" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>128300370</v>
       </c>
       <c r="B26" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300336</v>
+        <v>128300334</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>82979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898991</v>
+        <v>898973</v>
       </c>
       <c r="R2" t="n">
-        <v>7340368</v>
+        <v>7340375</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300334</v>
+        <v>128300336</v>
       </c>
       <c r="B3" t="n">
-        <v>82979</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898973</v>
+        <v>898991</v>
       </c>
       <c r="R3" t="n">
-        <v>7340375</v>
+        <v>7340368</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300365</v>
+        <v>128300368</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>898914</v>
+        <v>898675</v>
       </c>
       <c r="R4" t="n">
-        <v>7340380</v>
+        <v>7340362</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300368</v>
+        <v>128300382</v>
       </c>
       <c r="B5" t="n">
-        <v>79739</v>
+        <v>91469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>898675</v>
+        <v>898974</v>
       </c>
       <c r="R5" t="n">
-        <v>7340362</v>
+        <v>7340306</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128300382</v>
+        <v>128300365</v>
       </c>
       <c r="B6" t="n">
-        <v>91469</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>898974</v>
+        <v>898914</v>
       </c>
       <c r="R6" t="n">
-        <v>7340306</v>
+        <v>7340380</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128300342</v>
+        <v>128300330</v>
       </c>
       <c r="B10" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>899019</v>
+        <v>898890</v>
       </c>
       <c r="R10" t="n">
-        <v>7340290</v>
+        <v>7340453</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128300330</v>
+        <v>128300342</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>898890</v>
+        <v>899019</v>
       </c>
       <c r="R11" t="n">
-        <v>7340453</v>
+        <v>7340290</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300333</v>
+        <v>128300332</v>
       </c>
       <c r="B17" t="n">
-        <v>82979</v>
+        <v>97503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898956</v>
+        <v>898948</v>
       </c>
       <c r="R17" t="n">
-        <v>7340380</v>
+        <v>7340405</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128300332</v>
+        <v>128300333</v>
       </c>
       <c r="B19" t="n">
-        <v>97503</v>
+        <v>82979</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>898948</v>
+        <v>898956</v>
       </c>
       <c r="R19" t="n">
-        <v>7340405</v>
+        <v>7340380</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300334</v>
+        <v>128300336</v>
       </c>
       <c r="B2" t="n">
-        <v>82979</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898973</v>
+        <v>898991</v>
       </c>
       <c r="R2" t="n">
-        <v>7340375</v>
+        <v>7340368</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300336</v>
+        <v>128300334</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>82979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898991</v>
+        <v>898973</v>
       </c>
       <c r="R3" t="n">
-        <v>7340368</v>
+        <v>7340375</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -2130,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300332</v>
+        <v>128300385</v>
       </c>
       <c r="B17" t="n">
-        <v>97503</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898948</v>
+        <v>898974</v>
       </c>
       <c r="R17" t="n">
-        <v>7340405</v>
+        <v>7340314</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128300385</v>
+        <v>128300333</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>82979</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>898974</v>
+        <v>898956</v>
       </c>
       <c r="R18" t="n">
-        <v>7340314</v>
+        <v>7340380</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128300333</v>
+        <v>128300332</v>
       </c>
       <c r="B19" t="n">
-        <v>82979</v>
+        <v>97503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>898956</v>
+        <v>898948</v>
       </c>
       <c r="R19" t="n">
-        <v>7340380</v>
+        <v>7340405</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300336</v>
+        <v>128300334</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>82979</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898991</v>
+        <v>898973</v>
       </c>
       <c r="R2" t="n">
-        <v>7340368</v>
+        <v>7340375</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300334</v>
+        <v>128300336</v>
       </c>
       <c r="B3" t="n">
-        <v>82979</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898973</v>
+        <v>898991</v>
       </c>
       <c r="R3" t="n">
-        <v>7340375</v>
+        <v>7340368</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300368</v>
+        <v>128300382</v>
       </c>
       <c r="B4" t="n">
-        <v>79739</v>
+        <v>91469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>898675</v>
+        <v>898974</v>
       </c>
       <c r="R4" t="n">
-        <v>7340362</v>
+        <v>7340306</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300382</v>
+        <v>128300368</v>
       </c>
       <c r="B5" t="n">
-        <v>91469</v>
+        <v>79739</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>898974</v>
+        <v>898675</v>
       </c>
       <c r="R5" t="n">
-        <v>7340306</v>
+        <v>7340362</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128300386</v>
+        <v>128300381</v>
       </c>
       <c r="B8" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>898950</v>
+        <v>898984</v>
       </c>
       <c r="R8" t="n">
-        <v>7340336</v>
+        <v>7340282</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128300381</v>
+        <v>128300386</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>898984</v>
+        <v>898950</v>
       </c>
       <c r="R9" t="n">
-        <v>7340282</v>
+        <v>7340336</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128300330</v>
+        <v>128300342</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>898890</v>
+        <v>899019</v>
       </c>
       <c r="R10" t="n">
-        <v>7340453</v>
+        <v>7340290</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128300342</v>
+        <v>128300330</v>
       </c>
       <c r="B11" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>899019</v>
+        <v>898890</v>
       </c>
       <c r="R11" t="n">
-        <v>7340290</v>
+        <v>7340453</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300385</v>
+        <v>128300333</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>82979</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898974</v>
+        <v>898956</v>
       </c>
       <c r="R17" t="n">
-        <v>7340314</v>
+        <v>7340380</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128300333</v>
+        <v>128300385</v>
       </c>
       <c r="B18" t="n">
-        <v>82979</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>898956</v>
+        <v>898974</v>
       </c>
       <c r="R18" t="n">
-        <v>7340380</v>
+        <v>7340314</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128300331</v>
+        <v>128300369</v>
       </c>
       <c r="B24" t="n">
-        <v>79120</v>
+        <v>79739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>898938</v>
+        <v>898684</v>
       </c>
       <c r="R24" t="n">
-        <v>7340414</v>
+        <v>7340341</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128300369</v>
+        <v>128300370</v>
       </c>
       <c r="B25" t="n">
         <v>79739</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>898684</v>
+        <v>898703</v>
       </c>
       <c r="R25" t="n">
-        <v>7340341</v>
+        <v>7340339</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128300370</v>
+        <v>128300331</v>
       </c>
       <c r="B26" t="n">
-        <v>79739</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>898703</v>
+        <v>898938</v>
       </c>
       <c r="R26" t="n">
-        <v>7340339</v>
+        <v>7340414</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128300334</v>
+        <v>128300329</v>
       </c>
       <c r="B2" t="n">
-        <v>82979</v>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>898973</v>
+        <v>898852</v>
       </c>
       <c r="R2" t="n">
-        <v>7340375</v>
+        <v>7340468</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128300336</v>
+        <v>128300333</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>898991</v>
+        <v>898956</v>
       </c>
       <c r="R3" t="n">
-        <v>7340368</v>
+        <v>7340380</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128300382</v>
+        <v>128300334</v>
       </c>
       <c r="B4" t="n">
-        <v>91469</v>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>898974</v>
+        <v>898973</v>
       </c>
       <c r="R4" t="n">
-        <v>7340306</v>
+        <v>7340375</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128300368</v>
+        <v>128300383</v>
       </c>
       <c r="B5" t="n">
-        <v>79739</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>898675</v>
+        <v>898977</v>
       </c>
       <c r="R5" t="n">
-        <v>7340362</v>
+        <v>7340311</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128300365</v>
+        <v>128300366</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>898914</v>
+        <v>898886</v>
       </c>
       <c r="R6" t="n">
-        <v>7340380</v>
+        <v>7340369</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128300341</v>
+        <v>128300382</v>
       </c>
       <c r="B7" t="n">
-        <v>79120</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>899046</v>
+        <v>898974</v>
       </c>
       <c r="R7" t="n">
-        <v>7340303</v>
+        <v>7340306</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1257,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128300381</v>
+        <v>128300330</v>
       </c>
       <c r="B8" t="n">
-        <v>79120</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>898984</v>
+        <v>898890</v>
       </c>
       <c r="R8" t="n">
-        <v>7340282</v>
+        <v>7340453</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128300386</v>
+        <v>128300331</v>
       </c>
       <c r="B9" t="n">
-        <v>79739</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>898950</v>
+        <v>898938</v>
       </c>
       <c r="R9" t="n">
-        <v>7340336</v>
+        <v>7340414</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128300342</v>
+        <v>128300335</v>
       </c>
       <c r="B10" t="n">
-        <v>79739</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>899019</v>
+        <v>898975</v>
       </c>
       <c r="R10" t="n">
-        <v>7340290</v>
+        <v>7340373</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1548,14 +1548,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128300330</v>
+        <v>128300336</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>898890</v>
+        <v>898991</v>
       </c>
       <c r="R11" t="n">
-        <v>7340453</v>
+        <v>7340368</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,14 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128300335</v>
+        <v>128300364</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>898975</v>
+        <v>898946</v>
       </c>
       <c r="R12" t="n">
-        <v>7340373</v>
+        <v>7340339</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1742,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128300367</v>
+        <v>128300365</v>
       </c>
       <c r="B13" t="n">
-        <v>79144</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>898767</v>
+        <v>898914</v>
       </c>
       <c r="R13" t="n">
-        <v>7340393</v>
+        <v>7340380</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1839,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128300383</v>
+        <v>128300381</v>
       </c>
       <c r="B14" t="n">
-        <v>82979</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>898977</v>
+        <v>898984</v>
       </c>
       <c r="R14" t="n">
-        <v>7340311</v>
+        <v>7340282</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1936,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128300380</v>
+        <v>128300385</v>
       </c>
       <c r="B15" t="n">
-        <v>82979</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>899001</v>
+        <v>898974</v>
       </c>
       <c r="R15" t="n">
-        <v>7340285</v>
+        <v>7340314</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2033,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128300339</v>
+        <v>128300367</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>899026</v>
+        <v>898767</v>
       </c>
       <c r="R16" t="n">
-        <v>7340324</v>
+        <v>7340393</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128300333</v>
+        <v>128300368</v>
       </c>
       <c r="B17" t="n">
-        <v>82979</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,21 +2141,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>898956</v>
+        <v>898675</v>
       </c>
       <c r="R17" t="n">
-        <v>7340380</v>
+        <v>7340362</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128300385</v>
+        <v>128300369</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>898974</v>
+        <v>898684</v>
       </c>
       <c r="R18" t="n">
-        <v>7340314</v>
+        <v>7340341</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2324,32 +2324,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128300332</v>
+        <v>128300370</v>
       </c>
       <c r="B19" t="n">
-        <v>97503</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>898948</v>
+        <v>898703</v>
       </c>
       <c r="R19" t="n">
-        <v>7340405</v>
+        <v>7340339</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2421,32 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128300366</v>
+        <v>128300386</v>
       </c>
       <c r="B20" t="n">
-        <v>91469</v>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>898886</v>
+        <v>898950</v>
       </c>
       <c r="R20" t="n">
-        <v>7340369</v>
+        <v>7340336</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2518,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128300364</v>
+        <v>128300332</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>97983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>898946</v>
+        <v>898948</v>
       </c>
       <c r="R21" t="n">
-        <v>7340339</v>
+        <v>7340405</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2615,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128300340</v>
+        <v>128300380</v>
       </c>
       <c r="B22" t="n">
-        <v>97503</v>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>899041</v>
+        <v>899001</v>
       </c>
       <c r="R22" t="n">
-        <v>7340320</v>
+        <v>7340285</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2715,11 +2715,11 @@
         <v>128300338</v>
       </c>
       <c r="B23" t="n">
-        <v>79120</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2809,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128300369</v>
+        <v>128300339</v>
       </c>
       <c r="B24" t="n">
-        <v>79739</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>898684</v>
+        <v>899026</v>
       </c>
       <c r="R24" t="n">
-        <v>7340341</v>
+        <v>7340324</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2906,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128300370</v>
+        <v>128300341</v>
       </c>
       <c r="B25" t="n">
-        <v>79739</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>898703</v>
+        <v>899046</v>
       </c>
       <c r="R25" t="n">
-        <v>7340339</v>
+        <v>7340303</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128300331</v>
+        <v>128300342</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3014,21 +3014,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>898938</v>
+        <v>899019</v>
       </c>
       <c r="R26" t="n">
-        <v>7340414</v>
+        <v>7340290</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3097,6 +3097,103 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128300340</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hirvivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>899041</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7340320</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Haparanda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nedertorneå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Tyrén, Jan Apelqvist</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41136-2023 artfynd.xlsx
+++ b/artfynd/A 41136-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300329</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300333</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300334</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300380</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300383</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300366</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300382</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300330</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300331</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300335</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300336</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300338</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300339</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300341</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300364</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300365</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300381</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300385</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300367</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300342</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300368</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300369</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300370</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300386</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300332</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,8 +3324,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128300340</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>